--- a/OCT_2026/Oct_26.xlsx
+++ b/OCT_2026/Oct_26.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E62EE0-C0F3-4B19-B928-2E506BF2FB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814BD638-7829-40C5-BD5F-BB03A3EDD3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3948" uniqueCount="516">
   <si>
     <t>Sr.No</t>
   </si>
@@ -1461,9 +1461,6 @@
     <t>VTE</t>
   </si>
   <si>
-    <t>Lemon Tarka (ECO)</t>
-  </si>
-  <si>
     <t>BCE</t>
   </si>
   <si>
@@ -1600,6 +1597,12 @@
   </si>
   <si>
     <t>Booker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCN PROMO </t>
+  </si>
+  <si>
+    <t>Indomie Chicken ® 4 in 1</t>
   </si>
 </sst>
 </file>
@@ -7095,7 +7098,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -7138,7 +7141,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -7151,7 +7154,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P5</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -7166,7 +7169,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -7179,7 +7182,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -7188,7 +7191,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -7228,7 +7231,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -7245,7 +7248,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -7257,7 +7260,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -7314,7 +7317,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -7343,7 +7346,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -7407,7 +7410,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -7416,7 +7419,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -7430,7 +7433,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -7449,7 +7452,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -7461,7 +7464,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -7470,7 +7473,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -7481,7 +7484,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -7631,7 +7634,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -7704,7 +7707,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -7849,7 +7852,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -7995,27 +7998,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -8065,12 +8068,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -8082,7 +8085,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -8090,7 +8093,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -8515,7 +8518,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -8558,7 +8561,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -8571,7 +8574,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -8586,7 +8589,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -8599,7 +8602,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -8608,7 +8611,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -8648,7 +8651,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -8665,7 +8668,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -8677,7 +8680,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -8734,7 +8737,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -8763,7 +8766,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -8827,7 +8830,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -8836,7 +8839,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -8850,7 +8853,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -8869,7 +8872,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -8881,7 +8884,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -8890,7 +8893,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -8901,7 +8904,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -9051,7 +9054,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -9124,7 +9127,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -9269,7 +9272,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -9415,27 +9418,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -9485,12 +9488,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -9502,7 +9505,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -9510,7 +9513,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -9935,7 +9938,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -9978,7 +9981,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -9991,7 +9994,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -10006,7 +10009,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -10019,7 +10022,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -10028,7 +10031,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -10068,7 +10071,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -10085,7 +10088,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -10097,7 +10100,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -10154,7 +10157,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -10183,7 +10186,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -10247,7 +10250,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -10256,7 +10259,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -10270,7 +10273,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -10289,7 +10292,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -10301,7 +10304,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -10310,7 +10313,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -10321,7 +10324,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -10471,7 +10474,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -10544,7 +10547,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -10689,7 +10692,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -10835,27 +10838,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -10905,12 +10908,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -10922,7 +10925,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -10930,7 +10933,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -11355,7 +11358,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -11398,7 +11401,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -11411,7 +11414,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -11426,7 +11429,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -11439,7 +11442,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -11448,7 +11451,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -11488,7 +11491,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -11505,7 +11508,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -11517,7 +11520,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -11574,7 +11577,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -11603,7 +11606,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -11667,7 +11670,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -11676,7 +11679,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -11690,7 +11693,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -11709,7 +11712,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -11721,7 +11724,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -11730,7 +11733,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -11741,7 +11744,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -11891,7 +11894,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -11964,7 +11967,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -12109,7 +12112,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -12255,27 +12258,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -12325,12 +12328,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -12342,7 +12345,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -12350,7 +12353,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -12775,7 +12778,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -12818,7 +12821,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -12831,7 +12834,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -12846,7 +12849,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -12859,7 +12862,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -12868,7 +12871,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -12908,7 +12911,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -12925,7 +12928,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -12937,7 +12940,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -12994,7 +12997,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -13023,7 +13026,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -13087,7 +13090,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -13096,7 +13099,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -13110,7 +13113,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -13129,7 +13132,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -13141,7 +13144,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -13150,7 +13153,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -13161,7 +13164,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -13311,7 +13314,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -13384,7 +13387,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -13529,7 +13532,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -13675,27 +13678,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -13745,12 +13748,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -13762,7 +13765,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -13770,7 +13773,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -14195,7 +14198,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -14238,7 +14241,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -14251,7 +14254,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -14266,7 +14269,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -14279,7 +14282,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -14288,7 +14291,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -14328,7 +14331,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -14345,7 +14348,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -14357,7 +14360,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -14414,7 +14417,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -14443,7 +14446,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -14507,7 +14510,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -14516,7 +14519,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -14530,7 +14533,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -14549,7 +14552,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -14561,7 +14564,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -14570,7 +14573,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -14581,7 +14584,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -14731,7 +14734,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -14804,7 +14807,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -14949,7 +14952,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -15095,27 +15098,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -15165,12 +15168,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -15182,7 +15185,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -15190,7 +15193,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -15615,7 +15618,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -15658,7 +15661,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -15671,7 +15674,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -15686,7 +15689,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -15699,7 +15702,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -15708,7 +15711,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -15748,7 +15751,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -15765,7 +15768,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -15777,7 +15780,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -15834,7 +15837,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -15863,7 +15866,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -15927,7 +15930,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -15936,7 +15939,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -15950,7 +15953,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -15969,7 +15972,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -15981,7 +15984,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -15990,7 +15993,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -16001,7 +16004,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -16151,7 +16154,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -16224,7 +16227,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -16369,7 +16372,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -16515,27 +16518,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -16585,12 +16588,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -16602,7 +16605,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -16610,7 +16613,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -17035,7 +17038,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -17078,7 +17081,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -17091,7 +17094,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -17106,7 +17109,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -17119,7 +17122,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -17128,7 +17131,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -17168,7 +17171,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -17185,7 +17188,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -17197,7 +17200,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -17254,7 +17257,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -17283,7 +17286,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -17347,7 +17350,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -17356,7 +17359,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -17370,7 +17373,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -17389,7 +17392,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -17401,7 +17404,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -17410,7 +17413,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -17421,7 +17424,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -17571,7 +17574,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -17644,7 +17647,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -17789,7 +17792,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -17935,27 +17938,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -18005,12 +18008,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -18022,7 +18025,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -18030,7 +18033,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -18455,7 +18458,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -18498,7 +18501,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -18511,7 +18514,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -18526,7 +18529,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -18539,7 +18542,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -18548,7 +18551,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -18588,7 +18591,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -18605,7 +18608,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -18617,7 +18620,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -18674,7 +18677,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -18703,7 +18706,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -18767,7 +18770,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -18776,7 +18779,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -18790,7 +18793,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -18809,7 +18812,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -18821,7 +18824,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -18830,7 +18833,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -18841,7 +18844,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -18991,7 +18994,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -19064,7 +19067,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -19209,7 +19212,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -19355,27 +19358,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -19425,12 +19428,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -19442,7 +19445,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -19450,7 +19453,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -19875,7 +19878,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -19918,7 +19921,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -19931,7 +19934,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -19946,7 +19949,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -19959,7 +19962,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -19968,7 +19971,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -20008,7 +20011,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -20025,7 +20028,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -20037,7 +20040,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -20094,7 +20097,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -20123,7 +20126,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -20187,7 +20190,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -20196,7 +20199,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -20210,7 +20213,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -20229,7 +20232,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -20241,7 +20244,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -20250,7 +20253,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -20261,7 +20264,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -20411,7 +20414,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -20484,7 +20487,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -20629,7 +20632,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -20775,27 +20778,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -20845,12 +20848,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -20862,7 +20865,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -20870,7 +20873,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -23710,7 +23713,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -23753,7 +23756,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -23766,7 +23769,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -23781,7 +23784,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -23794,7 +23797,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -23803,7 +23806,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -23843,7 +23846,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -23860,7 +23863,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -23872,7 +23875,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -23929,7 +23932,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -23958,7 +23961,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -24022,7 +24025,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -24031,7 +24034,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -24045,7 +24048,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -24064,7 +24067,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -24076,7 +24079,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -24085,7 +24088,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -24096,7 +24099,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -24246,7 +24249,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -24319,7 +24322,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -24464,7 +24467,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -24610,27 +24613,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -24680,12 +24683,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -24697,7 +24700,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -24705,7 +24708,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -25130,7 +25133,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -25173,7 +25176,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -25186,7 +25189,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -25201,7 +25204,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -25214,7 +25217,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -25223,7 +25226,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -25263,7 +25266,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -25280,7 +25283,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -25292,7 +25295,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -25349,7 +25352,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -25378,7 +25381,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -25442,7 +25445,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -25451,7 +25454,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -25465,7 +25468,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -25484,7 +25487,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -25496,7 +25499,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -25505,7 +25508,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -25516,7 +25519,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -25666,7 +25669,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -25739,7 +25742,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -25884,7 +25887,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -26030,27 +26033,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -26100,12 +26103,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -26117,7 +26120,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -26125,7 +26128,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -26550,7 +26553,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -26593,7 +26596,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -26606,7 +26609,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -26621,7 +26624,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -26634,7 +26637,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -26643,7 +26646,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -26683,7 +26686,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -26700,7 +26703,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -26712,7 +26715,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -26769,7 +26772,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -26798,7 +26801,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -26862,7 +26865,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -26871,7 +26874,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -26885,7 +26888,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -26904,7 +26907,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -26916,7 +26919,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -26925,7 +26928,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -26936,7 +26939,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -27086,7 +27089,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -27159,7 +27162,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -27304,7 +27307,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -27450,27 +27453,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -27520,12 +27523,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -27537,7 +27540,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -27545,7 +27548,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -27970,7 +27973,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -28013,7 +28016,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -28026,7 +28029,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -28041,7 +28044,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -28054,7 +28057,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -28063,7 +28066,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -28103,7 +28106,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -28120,7 +28123,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -28132,7 +28135,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -28189,7 +28192,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -28218,7 +28221,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -28282,7 +28285,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -28291,7 +28294,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -28305,7 +28308,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -28324,7 +28327,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -28336,7 +28339,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -28345,7 +28348,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -28356,7 +28359,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -28506,7 +28509,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -28579,7 +28582,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -28724,7 +28727,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -28870,27 +28873,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -28940,12 +28943,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -28957,7 +28960,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -28965,7 +28968,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -29390,7 +29393,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -29433,7 +29436,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -29446,7 +29449,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -29461,7 +29464,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -29474,7 +29477,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -29483,7 +29486,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -29523,7 +29526,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -29540,7 +29543,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -29552,7 +29555,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -29609,7 +29612,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -29638,7 +29641,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -29702,7 +29705,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -29711,7 +29714,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -29725,7 +29728,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -29744,7 +29747,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -29756,7 +29759,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -29765,7 +29768,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -29776,7 +29779,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -29926,7 +29929,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -29999,7 +30002,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -30144,7 +30147,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -30290,27 +30293,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -30360,12 +30363,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -30377,7 +30380,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -30385,7 +30388,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -30810,7 +30813,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -30853,7 +30856,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -30866,7 +30869,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -30881,7 +30884,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -30894,7 +30897,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -30903,7 +30906,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -30943,7 +30946,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -30960,7 +30963,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -30972,7 +30975,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -31029,7 +31032,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -31058,7 +31061,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -31122,7 +31125,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -31131,7 +31134,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -31145,7 +31148,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -31164,7 +31167,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -31176,7 +31179,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -31185,7 +31188,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -31196,7 +31199,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -31346,7 +31349,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -31419,7 +31422,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -31564,7 +31567,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -31710,27 +31713,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -31780,12 +31783,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -31797,7 +31800,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -31805,7 +31808,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -32230,7 +32233,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -32273,7 +32276,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -32286,7 +32289,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -32301,7 +32304,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -32314,7 +32317,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -32323,7 +32326,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -32363,7 +32366,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -32380,7 +32383,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -32392,7 +32395,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -32449,7 +32452,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -32478,7 +32481,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -32542,7 +32545,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -32551,7 +32554,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -32565,7 +32568,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -32584,7 +32587,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -32596,7 +32599,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -32605,7 +32608,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -32616,7 +32619,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -32766,7 +32769,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -32839,7 +32842,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -32984,7 +32987,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -33130,27 +33133,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -33200,12 +33203,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -33217,7 +33220,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -33225,7 +33228,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -33650,7 +33653,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -33693,7 +33696,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -33706,7 +33709,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -33721,7 +33724,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -33734,7 +33737,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -33743,7 +33746,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -33783,7 +33786,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -33800,7 +33803,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -33812,7 +33815,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -33869,7 +33872,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -33898,7 +33901,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -33962,7 +33965,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -33971,7 +33974,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -33985,7 +33988,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -34004,7 +34007,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -34016,7 +34019,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -34025,7 +34028,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -34036,7 +34039,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -34186,7 +34189,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -34259,7 +34262,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -34404,7 +34407,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -34550,27 +34553,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -34620,12 +34623,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -34637,7 +34640,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -34645,7 +34648,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -35070,7 +35073,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -35113,7 +35116,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -35126,7 +35129,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -35141,7 +35144,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -35154,7 +35157,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -35163,7 +35166,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -35203,7 +35206,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -35220,7 +35223,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -35232,7 +35235,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -35289,7 +35292,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -35318,7 +35321,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -35382,7 +35385,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -35391,7 +35394,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -35405,7 +35408,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -35424,7 +35427,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -35436,7 +35439,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -35445,7 +35448,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -35456,7 +35459,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -35606,7 +35609,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -35679,7 +35682,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -35824,7 +35827,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -35970,27 +35973,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -36040,12 +36043,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -36057,7 +36060,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -36065,7 +36068,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -36490,7 +36493,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -36533,7 +36536,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -36546,7 +36549,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -36561,7 +36564,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -36574,7 +36577,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -36583,7 +36586,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -36623,7 +36626,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -36640,7 +36643,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -36652,7 +36655,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -36709,7 +36712,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -36738,7 +36741,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -36802,7 +36805,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -36811,7 +36814,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -36825,7 +36828,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -36844,7 +36847,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -36856,7 +36859,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -36865,7 +36868,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -36876,7 +36879,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -37026,7 +37029,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -37099,7 +37102,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -37244,7 +37247,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -37390,27 +37393,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -37460,12 +37463,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -37477,7 +37480,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -37485,7 +37488,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -37897,28 +37900,28 @@
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.1796875" style="163" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="4.81640625" style="163" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="163" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" style="163" customWidth="1"/>
     <col min="5" max="5" width="23.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.81640625" style="164" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.81640625" style="164" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.453125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.453125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.453125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.453125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="16.54296875" bestFit="1" customWidth="1"/>
   </cols>
@@ -38090,10 +38093,10 @@
       </c>
       <c r="B6" s="166"/>
       <c r="C6" s="166" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D6" s="166" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E6" s="178" t="s">
         <v>454</v>
@@ -38277,10 +38280,10 @@
       </c>
       <c r="B8" s="166"/>
       <c r="C8" s="166" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D8" s="166" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E8" s="178" t="s">
         <v>458</v>
@@ -38368,10 +38371,10 @@
       </c>
       <c r="B9" s="166"/>
       <c r="C9" s="166" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D9" s="166" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E9" s="178" t="s">
         <v>460</v>
@@ -38556,10 +38559,10 @@
       </c>
       <c r="B11" s="166"/>
       <c r="C11" s="166" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D11" s="166" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E11" s="178" t="s">
         <v>464</v>
@@ -38744,49 +38747,47 @@
       </c>
       <c r="B13" s="166"/>
       <c r="C13" s="166" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="D13" s="166" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="E13" s="178" t="s">
-        <v>468</v>
+        <v>515</v>
       </c>
       <c r="F13" s="179">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G13" s="180">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H13" s="180">
         <f t="shared" si="2"/>
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="I13" s="181">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J13" s="181">
         <f t="shared" si="3"/>
-        <v>1914.4240000000002</v>
+        <v>2363.1887999999999</v>
       </c>
       <c r="K13" s="181">
         <f t="shared" si="12"/>
-        <v>47.860600000000005</v>
+        <v>196.93239999999997</v>
       </c>
       <c r="L13" s="182">
-        <v>1569.2</v>
+        <v>1937.04</v>
       </c>
       <c r="M13" s="182">
         <f t="shared" si="4"/>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="N13" s="183">
-        <f t="shared" si="13"/>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="O13" s="184">
-        <f t="shared" si="5"/>
-        <v>4.3153000000000006</v>
+        <v>5.8</v>
       </c>
       <c r="P13" s="185"/>
       <c r="Q13" s="184">
@@ -38800,31 +38801,31 @@
       </c>
       <c r="T13" s="182">
         <f t="shared" si="8"/>
-        <v>1396.5880000000002</v>
+        <v>1867.4399999999996</v>
       </c>
       <c r="U13" s="182">
         <f t="shared" si="9"/>
-        <v>34.914700000000003</v>
+        <v>155.61999999999998</v>
       </c>
       <c r="V13" s="182">
         <f t="shared" si="10"/>
-        <v>251.38584000000003</v>
+        <v>336.1391999999999</v>
       </c>
       <c r="W13" s="182">
         <f t="shared" si="10"/>
-        <v>6.2846460000000004</v>
+        <v>28.011599999999994</v>
       </c>
       <c r="X13" s="182">
         <f t="shared" si="0"/>
-        <v>1647.9738400000001</v>
+        <v>2203.5791999999997</v>
       </c>
       <c r="Y13" s="182">
         <f t="shared" si="0"/>
-        <v>41.199346000000006</v>
+        <v>183.63159999999996</v>
       </c>
       <c r="AA13" s="182">
         <f t="shared" si="1"/>
-        <v>2.4</v>
+        <v>0.84</v>
       </c>
       <c r="AC13" s="251">
         <f>SUM(AC6:AC12)</f>
@@ -38838,49 +38839,49 @@
       </c>
       <c r="B14" s="166"/>
       <c r="C14" s="166" t="s">
+        <v>468</v>
+      </c>
+      <c r="D14" s="166" t="s">
+        <v>468</v>
+      </c>
+      <c r="E14" s="178" t="s">
         <v>469</v>
-      </c>
-      <c r="D14" s="166" t="s">
-        <v>469</v>
-      </c>
-      <c r="E14" s="178" t="s">
-        <v>470</v>
       </c>
       <c r="F14" s="179">
         <v>60</v>
       </c>
       <c r="G14" s="180">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H14" s="180">
         <f t="shared" si="2"/>
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="I14" s="181">
         <v>50</v>
       </c>
       <c r="J14" s="181">
         <f t="shared" si="3"/>
-        <v>1914.4240000000002</v>
+        <v>1914.424</v>
       </c>
       <c r="K14" s="181">
         <f t="shared" si="12"/>
-        <v>47.860600000000005</v>
+        <v>39.883833333333335</v>
       </c>
       <c r="L14" s="182">
         <v>1569.2</v>
       </c>
       <c r="M14" s="182">
         <f t="shared" si="4"/>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="N14" s="183">
         <f t="shared" si="13"/>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="O14" s="184">
         <f t="shared" si="5"/>
-        <v>4.3153000000000006</v>
+        <v>3.923</v>
       </c>
       <c r="P14" s="185"/>
       <c r="Q14" s="184">
@@ -38894,31 +38895,31 @@
       </c>
       <c r="T14" s="182">
         <f t="shared" si="8"/>
-        <v>1396.5880000000002</v>
+        <v>1380.8960000000002</v>
       </c>
       <c r="U14" s="182">
         <f t="shared" si="9"/>
-        <v>34.914700000000003</v>
+        <v>28.768666666666668</v>
       </c>
       <c r="V14" s="182">
         <f t="shared" si="10"/>
-        <v>251.38584000000003</v>
+        <v>248.56128000000001</v>
       </c>
       <c r="W14" s="182">
         <f t="shared" si="10"/>
-        <v>6.2846460000000004</v>
+        <v>5.1783600000000005</v>
       </c>
       <c r="X14" s="182">
         <f t="shared" si="0"/>
-        <v>1647.9738400000001</v>
+        <v>1629.4572800000001</v>
       </c>
       <c r="Y14" s="182">
         <f t="shared" si="0"/>
-        <v>41.199346000000006</v>
+        <v>33.947026666666666</v>
       </c>
       <c r="AA14" s="182">
         <f t="shared" si="1"/>
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="15" spans="1:29" s="197" customFormat="1" x14ac:dyDescent="0.35">
@@ -40683,7 +40684,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -40726,7 +40727,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -40739,7 +40740,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -40754,7 +40755,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -40767,7 +40768,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -40776,7 +40777,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -40816,7 +40817,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -40833,7 +40834,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -40845,7 +40846,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -40902,7 +40903,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -40931,7 +40932,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -40995,7 +40996,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -41004,7 +41005,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -41018,7 +41019,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -41037,7 +41038,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -41049,7 +41050,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -41058,7 +41059,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -41069,7 +41070,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -41219,7 +41220,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -41292,7 +41293,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -41437,7 +41438,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -41583,27 +41584,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -41653,12 +41654,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -41670,7 +41671,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -41678,7 +41679,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -42103,7 +42104,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -42146,7 +42147,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -42159,7 +42160,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -42174,7 +42175,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -42187,7 +42188,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -42196,7 +42197,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -42236,7 +42237,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -42253,7 +42254,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -42265,7 +42266,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -42322,7 +42323,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -42351,7 +42352,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -42415,7 +42416,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -42424,7 +42425,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -42438,7 +42439,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -42457,7 +42458,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -42469,7 +42470,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -42478,7 +42479,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -42489,7 +42490,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -42639,7 +42640,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -42712,7 +42713,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -42857,7 +42858,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -43003,27 +43004,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -43073,12 +43074,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -43090,7 +43091,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -43098,7 +43099,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -43523,7 +43524,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -43566,7 +43567,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -43579,7 +43580,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -43594,7 +43595,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -43607,7 +43608,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -43616,7 +43617,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -43656,7 +43657,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -43673,7 +43674,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -43685,7 +43686,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -43742,7 +43743,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -43771,7 +43772,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -43835,7 +43836,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -43844,7 +43845,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -43858,7 +43859,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -43877,7 +43878,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -43889,7 +43890,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -43898,7 +43899,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -43909,7 +43910,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -44059,7 +44060,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -44132,7 +44133,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -44277,7 +44278,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -44423,27 +44424,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -44493,12 +44494,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -44510,7 +44511,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -44518,7 +44519,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -44943,7 +44944,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -44986,7 +44987,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -44999,7 +45000,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -45014,7 +45015,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -45027,7 +45028,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -45036,7 +45037,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -45076,7 +45077,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -45093,7 +45094,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -45105,7 +45106,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -45162,7 +45163,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -45191,7 +45192,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -45255,7 +45256,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -45264,7 +45265,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -45278,7 +45279,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -45297,7 +45298,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -45309,7 +45310,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -45318,7 +45319,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -45329,7 +45330,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -45479,7 +45480,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -45552,7 +45553,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -45697,7 +45698,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -45843,27 +45844,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -45913,12 +45914,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -45930,7 +45931,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -45938,7 +45939,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -46363,7 +46364,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -46406,7 +46407,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -46419,7 +46420,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -46434,7 +46435,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -46447,7 +46448,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -46456,7 +46457,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -46496,7 +46497,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -46513,7 +46514,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -46525,7 +46526,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -46582,7 +46583,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -46611,7 +46612,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -46675,7 +46676,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -46684,7 +46685,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -46698,7 +46699,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -46717,7 +46718,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -46729,7 +46730,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -46738,7 +46739,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -46749,7 +46750,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -46899,7 +46900,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -46972,7 +46973,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -47117,7 +47118,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -47263,27 +47264,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -47333,12 +47334,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -47350,7 +47351,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -47358,7 +47359,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -47833,7 +47834,7 @@
       <c r="L4" s="371"/>
       <c r="M4" s="401">
         <f ca="1">TODAY()+1</f>
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="N4" s="401"/>
       <c r="O4" s="401"/>
@@ -47861,7 +47862,7 @@
       <c r="L5" s="371"/>
       <c r="M5" s="401">
         <f ca="1">M4-1</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="N5" s="370"/>
       <c r="O5" s="370"/>
@@ -47993,7 +47994,7 @@
     </row>
     <row r="11" spans="1:18 16382:16383" x14ac:dyDescent="0.35">
       <c r="A11" s="134" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="241" t="s">
         <v>81</v>
@@ -48020,7 +48021,7 @@
     </row>
     <row r="12" spans="1:18 16382:16383" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>78</v>
@@ -48146,7 +48147,7 @@
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v xml:space="preserve">Meat Masala </v>
+        <v>Chicken Chatkhara</v>
       </c>
       <c r="C16" s="105">
         <f>VLOOKUP(A16,'Cust. Price List'!D6:M14,3,0)</f>
@@ -48264,53 +48265,53 @@
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Chicken Chatkhara</v>
-      </c>
-      <c r="C18" s="106">
+        <v xml:space="preserve">Meat Masala </v>
+      </c>
+      <c r="C18" s="106" t="e">
         <f>VLOOKUP(B18,'Cust. Price List'!E8:P16,2,0)</f>
-        <v>70</v>
-      </c>
-      <c r="D18" s="92">
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="92" t="e">
         <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E18" s="92">
+        <v>#N/A</v>
+      </c>
+      <c r="E18" s="92" t="e">
         <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,6,0)</f>
-        <v>65</v>
-      </c>
-      <c r="F18" s="263">
+        <v>#N/A</v>
+      </c>
+      <c r="F18" s="263" t="e">
         <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,10,0)</f>
-        <v>52.462499999999999</v>
+        <v>#N/A</v>
       </c>
       <c r="G18" s="83"/>
       <c r="H18" s="96"/>
-      <c r="I18" s="236">
+      <c r="I18" s="236" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="128">
+        <v>#N/A</v>
+      </c>
+      <c r="J18" s="128" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="230">
+        <v>#N/A</v>
+      </c>
+      <c r="K18" s="119" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L18" s="230" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="230">
+        <v>#N/A</v>
+      </c>
+      <c r="M18" s="230" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="239">
+        <v>#N/A</v>
+      </c>
+      <c r="N18" s="239" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="119">
+        <v>#N/A</v>
+      </c>
+      <c r="O18" s="119" t="e">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="19" spans="1:18 16383:16383" x14ac:dyDescent="0.35">
@@ -48319,7 +48320,7 @@
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Meat Masala (Jumbo)</v>
+        <v>Chicken Chatkhara (Jumbo)</v>
       </c>
       <c r="C19" s="106">
         <f>VLOOKUP(B19,'Cust. Price List'!E9:P17,2,0)</f>
@@ -48431,53 +48432,53 @@
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Chicken Chatkhara (Jumbo)</v>
-      </c>
-      <c r="C21" s="106">
+        <v>Meat Masala (Jumbo)</v>
+      </c>
+      <c r="C21" s="106" t="e">
         <f>VLOOKUP(B21,'Cust. Price List'!E11:P19,2,0)</f>
-        <v>120</v>
-      </c>
-      <c r="D21" s="92">
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="92" t="e">
         <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E21" s="92">
+        <v>#N/A</v>
+      </c>
+      <c r="E21" s="92" t="e">
         <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,6,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F21" s="263">
+        <v>#N/A</v>
+      </c>
+      <c r="F21" s="263" t="e">
         <f>VLOOKUP(A21,'Cust. Price List'!D11:M19,10,0)</f>
-        <v>72.64</v>
+        <v>#N/A</v>
       </c>
       <c r="G21" s="83"/>
       <c r="H21" s="96"/>
-      <c r="I21" s="236">
+      <c r="I21" s="236" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="128">
+        <v>#N/A</v>
+      </c>
+      <c r="J21" s="128" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="230">
+        <v>#N/A</v>
+      </c>
+      <c r="K21" s="119" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L21" s="230" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="230">
+        <v>#N/A</v>
+      </c>
+      <c r="M21" s="230" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="239">
+        <v>#N/A</v>
+      </c>
+      <c r="N21" s="239" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="119">
+        <v>#N/A</v>
+      </c>
+      <c r="O21" s="119" t="e">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" spans="1:18 16383:16383" x14ac:dyDescent="0.35">
@@ -48539,60 +48540,60 @@
       <c r="A23" s="82" t="s">
         <v>467</v>
       </c>
-      <c r="B23" s="109" t="str">
+      <c r="B23" s="109" t="e">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
-      </c>
-      <c r="C23" s="106">
+        <v>#N/A</v>
+      </c>
+      <c r="C23" s="106" t="e">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
-      </c>
-      <c r="D23" s="92">
+        <v>#N/A</v>
+      </c>
+      <c r="D23" s="92" t="e">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
-      </c>
-      <c r="E23" s="92">
+        <v>#N/A</v>
+      </c>
+      <c r="E23" s="92" t="e">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F23" s="263">
+        <v>#N/A</v>
+      </c>
+      <c r="F23" s="263" t="e">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>#N/A</v>
       </c>
       <c r="G23" s="83"/>
       <c r="H23" s="96"/>
-      <c r="I23" s="236">
+      <c r="I23" s="236" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="128">
+        <v>#N/A</v>
+      </c>
+      <c r="J23" s="128" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="230">
+        <v>#N/A</v>
+      </c>
+      <c r="K23" s="119" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L23" s="230" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="230">
+        <v>#N/A</v>
+      </c>
+      <c r="M23" s="230" t="e">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="239">
+        <v>#N/A</v>
+      </c>
+      <c r="N23" s="239" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="119">
+        <v>#N/A</v>
+      </c>
+      <c r="O23" s="119" t="e">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="24" spans="1:18 16383:16383" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -48604,7 +48605,7 @@
       </c>
       <c r="D24" s="98">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="98">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -48612,7 +48613,7 @@
       </c>
       <c r="F24" s="264">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="84"/>
       <c r="H24" s="97"/>
@@ -48665,33 +48666,33 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="I25" s="114">
+      <c r="I25" s="114" t="e">
         <f t="shared" si="7"/>
-        <v>1452.8</v>
-      </c>
-      <c r="J25" s="101">
+        <v>#N/A</v>
+      </c>
+      <c r="J25" s="101" t="e">
         <f t="shared" si="7"/>
-        <v>50.848000000000006</v>
-      </c>
-      <c r="K25" s="102">
+        <v>#N/A</v>
+      </c>
+      <c r="K25" s="102" t="e">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="232">
+        <v>#N/A</v>
+      </c>
+      <c r="L25" s="232" t="e">
         <f t="shared" si="7"/>
-        <v>1401.952</v>
-      </c>
-      <c r="M25" s="233">
+        <v>#N/A</v>
+      </c>
+      <c r="M25" s="233" t="e">
         <f>SUM(M16:M24)</f>
-        <v>308.42944</v>
-      </c>
-      <c r="N25" s="101">
+        <v>#N/A</v>
+      </c>
+      <c r="N25" s="101" t="e">
         <f>SUM(N16:N24)</f>
-        <v>42.759536000000004</v>
-      </c>
-      <c r="O25" s="234">
+        <v>#N/A</v>
+      </c>
+      <c r="O25" s="234" t="e">
         <f>SUM(O16:O24)</f>
-        <v>1753.1409760000001</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="26" spans="1:18 16383:16383" x14ac:dyDescent="0.35">
@@ -48738,9 +48739,9 @@
         <v>60</v>
       </c>
       <c r="N28" s="385"/>
-      <c r="O28" s="139">
+      <c r="O28" s="139" t="e">
         <f>I25</f>
-        <v>1452.8</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="29" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -48758,9 +48759,9 @@
         <v>85</v>
       </c>
       <c r="N29" s="387"/>
-      <c r="O29" s="140">
+      <c r="O29" s="140" t="e">
         <f>K25</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -48778,9 +48779,9 @@
         <v>86</v>
       </c>
       <c r="N30" s="387"/>
-      <c r="O30" s="140">
+      <c r="O30" s="140" t="e">
         <f>J25</f>
-        <v>50.848000000000006</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="31" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -48799,9 +48800,9 @@
         <v>87</v>
       </c>
       <c r="N31" s="387"/>
-      <c r="O31" s="140">
+      <c r="O31" s="140" t="e">
         <f>O28-O29-O30</f>
-        <v>1401.952</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="32" spans="1:18 16383:16383" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -48823,9 +48824,9 @@
         <f>IF(B12="Registered",18%,22%)</f>
         <v>0.22</v>
       </c>
-      <c r="O32" s="140">
+      <c r="O32" s="140" t="e">
         <f>N32*O31</f>
-        <v>308.42944</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -48844,9 +48845,9 @@
         <v>76</v>
       </c>
       <c r="N33" s="389"/>
-      <c r="O33" s="140">
+      <c r="O33" s="140" t="e">
         <f>O31+O32</f>
-        <v>1710.3814400000001</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="34" spans="2:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -48868,9 +48869,9 @@
         <f>IF(B11="Filer",0.5%,2.5%)</f>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="O34" s="140">
+      <c r="O34" s="140" t="e">
         <f>N34*O33</f>
-        <v>42.759536000000004</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="35" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -48878,9 +48879,9 @@
         <v>88</v>
       </c>
       <c r="N35" s="346"/>
-      <c r="O35" s="141">
+      <c r="O35" s="141" t="e">
         <f>O28-O29+O31+O34</f>
-        <v>2897.511536</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="36" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -49018,7 +49019,7 @@
       </c>
       <c r="L1" s="411"/>
       <c r="M1" s="406" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N1" s="407"/>
       <c r="O1" s="408"/>
@@ -49051,13 +49052,13 @@
         <v>451</v>
       </c>
       <c r="M2" s="242" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N2" s="242" t="s">
+        <v>481</v>
+      </c>
+      <c r="O2" s="242" t="s">
         <v>482</v>
-      </c>
-      <c r="O2" s="242" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="3" spans="3:24" x14ac:dyDescent="0.35">
@@ -49200,17 +49201,17 @@
     </row>
     <row r="6" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C6" s="409" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D6" s="409"/>
       <c r="E6" s="409"/>
       <c r="F6" s="409"/>
       <c r="G6" s="409"/>
       <c r="T6" s="257" t="s">
+        <v>486</v>
+      </c>
+      <c r="U6" s="257" t="s">
         <v>487</v>
-      </c>
-      <c r="U6" s="257" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="7" spans="3:24" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -49237,27 +49238,27 @@
       </c>
       <c r="L7" s="340"/>
       <c r="M7" s="406" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N7" s="407"/>
       <c r="O7" s="408"/>
       <c r="P7" s="256" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q7" s="242" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="R7" s="404" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="S7" s="404" t="s">
+        <v>484</v>
+      </c>
+      <c r="T7" s="402" t="s">
         <v>485</v>
       </c>
-      <c r="T7" s="402" t="s">
-        <v>486</v>
-      </c>
       <c r="U7" s="402" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="3:24" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -49288,19 +49289,19 @@
         <v>451</v>
       </c>
       <c r="M8" s="242" t="s">
+        <v>470</v>
+      </c>
+      <c r="N8" s="242" t="s">
+        <v>481</v>
+      </c>
+      <c r="O8" s="242" t="s">
+        <v>482</v>
+      </c>
+      <c r="P8" s="242" t="s">
         <v>471</v>
       </c>
-      <c r="N8" s="242" t="s">
-        <v>482</v>
-      </c>
-      <c r="O8" s="242" t="s">
-        <v>483</v>
-      </c>
-      <c r="P8" s="242" t="s">
-        <v>472</v>
-      </c>
       <c r="Q8" s="242" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="R8" s="404"/>
       <c r="S8" s="404"/>
@@ -49513,7 +49514,7 @@
     </row>
     <row r="12" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C12" s="410" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D12" s="410"/>
       <c r="E12" s="410"/>
@@ -49544,27 +49545,27 @@
       </c>
       <c r="L13" s="340"/>
       <c r="M13" s="406" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N13" s="407"/>
       <c r="O13" s="408"/>
       <c r="P13" s="256" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q13" s="242" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="R13" s="404" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="S13" s="404" t="s">
+        <v>484</v>
+      </c>
+      <c r="T13" s="402" t="s">
         <v>485</v>
       </c>
-      <c r="T13" s="402" t="s">
-        <v>486</v>
-      </c>
       <c r="U13" s="402" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="3:24" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -49595,19 +49596,19 @@
         <v>451</v>
       </c>
       <c r="M14" s="242" t="s">
+        <v>470</v>
+      </c>
+      <c r="N14" s="242" t="s">
+        <v>481</v>
+      </c>
+      <c r="O14" s="242" t="s">
+        <v>482</v>
+      </c>
+      <c r="P14" s="242" t="s">
         <v>471</v>
       </c>
-      <c r="N14" s="242" t="s">
-        <v>482</v>
-      </c>
-      <c r="O14" s="242" t="s">
-        <v>483</v>
-      </c>
-      <c r="P14" s="242" t="s">
-        <v>472</v>
-      </c>
       <c r="Q14" s="242" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="R14" s="404"/>
       <c r="S14" s="404"/>
@@ -49820,7 +49821,7 @@
     </row>
     <row r="19" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C19" s="409" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D19" s="409"/>
       <c r="E19" s="409"/>
@@ -49851,27 +49852,27 @@
       </c>
       <c r="L20" s="340"/>
       <c r="M20" s="406" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N20" s="407"/>
       <c r="O20" s="408"/>
       <c r="P20" s="256" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q20" s="242" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="R20" s="404" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="S20" s="404" t="s">
+        <v>484</v>
+      </c>
+      <c r="T20" s="402" t="s">
         <v>485</v>
       </c>
-      <c r="T20" s="402" t="s">
-        <v>486</v>
-      </c>
       <c r="U20" s="402" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="21" spans="3:21" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -49902,19 +49903,19 @@
         <v>451</v>
       </c>
       <c r="M21" s="242" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N21" s="242" t="s">
+        <v>481</v>
+      </c>
+      <c r="O21" s="242" t="s">
         <v>482</v>
       </c>
-      <c r="O21" s="242" t="s">
-        <v>483</v>
-      </c>
       <c r="P21" s="242" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q21" s="242" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="R21" s="404"/>
       <c r="S21" s="404"/>
@@ -50145,7 +50146,7 @@
     </row>
     <row r="26" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C26" s="409" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D26" s="409"/>
       <c r="E26" s="409"/>
@@ -50176,27 +50177,27 @@
       </c>
       <c r="L27" s="340"/>
       <c r="M27" s="406" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N27" s="407"/>
       <c r="O27" s="408"/>
       <c r="P27" s="256" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q27" s="242" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="R27" s="404" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="S27" s="404" t="s">
+        <v>484</v>
+      </c>
+      <c r="T27" s="402" t="s">
         <v>485</v>
       </c>
-      <c r="T27" s="402" t="s">
-        <v>486</v>
-      </c>
       <c r="U27" s="402" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="28" spans="3:21" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -50227,19 +50228,19 @@
         <v>451</v>
       </c>
       <c r="M28" s="242" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N28" s="242" t="s">
+        <v>481</v>
+      </c>
+      <c r="O28" s="242" t="s">
         <v>482</v>
       </c>
-      <c r="O28" s="242" t="s">
-        <v>483</v>
-      </c>
       <c r="P28" s="242" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q28" s="242" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="R28" s="404"/>
       <c r="S28" s="404"/>
@@ -50600,7 +50601,7 @@
       </c>
       <c r="K1" s="411"/>
       <c r="L1" s="406" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M1" s="407"/>
       <c r="N1" s="408"/>
@@ -50633,19 +50634,19 @@
         <v>451</v>
       </c>
       <c r="L2" s="242" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M2" s="242" t="s">
+        <v>481</v>
+      </c>
+      <c r="N2" s="242" t="s">
         <v>482</v>
       </c>
-      <c r="N2" s="242" t="s">
-        <v>483</v>
-      </c>
       <c r="P2" s="242" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q2" s="259" t="s">
         <v>490</v>
-      </c>
-      <c r="Q2" s="259" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
@@ -54009,14 +54010,14 @@
     <col min="6" max="6" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.453125" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.90625" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" customWidth="1"/>
     <col min="11" max="11" width="6.54296875" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="9" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="8" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="9.1796875" style="61" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="7.81640625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.6328125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.54296875" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="28.7265625" customWidth="1"/>
@@ -54031,17 +54032,17 @@
       <c r="B2" s="369"/>
       <c r="C2" s="369"/>
       <c r="E2" s="356" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F2" s="357"/>
       <c r="G2" s="357"/>
       <c r="H2" s="354" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I2" s="354"/>
       <c r="J2" s="355"/>
       <c r="R2" s="351" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="S2" s="352"/>
       <c r="T2" s="353"/>
@@ -54053,12 +54054,12 @@
       <c r="B3" s="370"/>
       <c r="C3" s="370"/>
       <c r="E3" s="360" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F3" s="361"/>
       <c r="G3" s="361"/>
       <c r="H3" s="358">
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="I3" s="358"/>
       <c r="J3" s="359"/>
@@ -54141,7 +54142,7 @@
         <v>84</v>
       </c>
       <c r="N5" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O5" s="103" t="s">
         <v>89</v>
@@ -54150,7 +54151,7 @@
         <v>56</v>
       </c>
       <c r="Q5" s="314" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="R5" s="313">
         <v>3</v>
@@ -54175,7 +54176,7 @@
         <v>57</v>
       </c>
       <c r="E6" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F6" s="145" t="s">
         <v>53</v>
@@ -54194,7 +54195,7 @@
         <v>39</v>
       </c>
       <c r="L6" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M6" s="363"/>
       <c r="N6" s="365"/>
@@ -54206,7 +54207,7 @@
         <v>38</v>
       </c>
       <c r="Q6" s="314" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="R6" s="313">
         <v>4</v>
@@ -54225,7 +54226,7 @@
     </row>
     <row r="7" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B7" s="306" t="str">
         <f>VLOOKUP($A7,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -54391,7 +54392,7 @@
     </row>
     <row r="9" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B9" s="307" t="str">
         <f>VLOOKUP($A9,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -54471,7 +54472,7 @@
     </row>
     <row r="10" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B10" s="307" t="str">
         <f>VLOOKUP($A10,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -54631,7 +54632,7 @@
     </row>
     <row r="12" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B12" s="307" t="str">
         <f>VLOOKUP($A12,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -54791,27 +54792,27 @@
     </row>
     <row r="14" spans="1:20 16377:16378" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B14" s="307" t="str">
         <f>VLOOKUP($A14,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C14" s="106">
         <f>VLOOKUP(B14,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D14" s="284">
         <f>VLOOKUP(A14,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E14" s="291">
         <f>VLOOKUP(A14,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F14" s="292">
         <f>VLOOKUP(A14,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G14" s="286">
         <f>+'1'!G23+'2'!G23+'3'!G23+'4'!G23+'5'!G23+'6'!G23+'7'!G23+'8'!G23+'9'!G23+'10'!G23+'11'!G23+'12'!G23+'13'!G23+'14'!G23+'15'!G23+'16'!G23+'17'!G23+'18'!G23+'19'!G23+'20'!G23+'21'!G23+'22'!G23+'23'!G23+'24'!G23+'25'!G23+'26'!G23+'27'!G23+'28'!G23+'29'!G23+'30'!G23</f>
@@ -54871,7 +54872,7 @@
     </row>
     <row r="15" spans="1:20 16377:16378" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B15" s="308" t="str">
         <f>VLOOKUP($A15,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -54883,7 +54884,7 @@
       </c>
       <c r="D15" s="285">
         <f>VLOOKUP(A15,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E15" s="293">
         <f>VLOOKUP(A15,'Cust. Price List'!D14:M22,6,0)</f>
@@ -54891,7 +54892,7 @@
       </c>
       <c r="F15" s="294">
         <f>VLOOKUP(A15,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G15" s="286">
         <f>+'1'!G24+'2'!G24+'3'!G24+'4'!G24+'5'!G24+'6'!G24+'7'!G24+'8'!G24+'9'!G24+'10'!G24+'11'!G24+'12'!G24+'13'!G24+'14'!G24+'15'!G24+'16'!G24+'17'!G24+'18'!G24+'19'!G24+'20'!G24+'21'!G24+'22'!G24+'23'!G24+'24'!G24+'25'!G24+'26'!G24+'27'!G24+'28'!G24+'29'!G24+'30'!G24</f>
@@ -55418,7 +55419,7 @@
     <row r="33" spans="2:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="R33" s="303"/>
       <c r="S33" s="302" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
@@ -55427,42 +55428,42 @@
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -55507,7 +55508,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:XFD38"/>
+  <dimension ref="A2:XFD48"/>
   <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
@@ -55516,13 +55517,13 @@
     <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.453125" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.54296875" customWidth="1"/>
     <col min="10" max="10" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -55565,7 +55566,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -55578,7 +55579,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>Summary!H3</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -55593,7 +55594,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -55606,7 +55607,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -55615,7 +55616,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -55655,7 +55656,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -55672,7 +55673,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -55684,7 +55685,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -55741,7 +55742,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -55770,7 +55771,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -55834,7 +55835,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -55843,7 +55844,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="317" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -55857,7 +55858,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -55876,7 +55877,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -55888,7 +55889,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="317" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -55897,7 +55898,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -55908,7 +55909,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -56058,7 +56059,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -56131,7 +56132,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -56276,7 +56277,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -56407,10 +56408,10 @@
       </c>
       <c r="Q22" s="319"/>
       <c r="S22" s="269">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="T22" s="270">
-        <v>3.5000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="U22" s="270">
         <v>5.0999999999999997E-2</v>
@@ -56422,27 +56423,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -56480,24 +56481,20 @@
       </c>
       <c r="Q23" s="319"/>
       <c r="S23" s="269">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="T23" s="270">
-        <f>+T22</f>
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="U23" s="270">
-        <f>+U22</f>
-        <v>5.0999999999999997E-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U23" s="270"/>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -56509,7 +56506,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -56517,7 +56514,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -56559,11 +56556,11 @@
       </c>
       <c r="T24" s="270">
         <f>+T23</f>
-        <v>3.5000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="U24" s="270">
         <f>+U23</f>
-        <v>5.0999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="V24" s="142">
         <f t="shared" si="6"/>
@@ -56840,6 +56837,29 @@
     <row r="38" spans="2:16" x14ac:dyDescent="0.35">
       <c r="L38">
         <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="H46">
+        <v>161.41999999999999</v>
+      </c>
+      <c r="I46" s="131">
+        <v>0.08</v>
+      </c>
+      <c r="J46" s="131"/>
+      <c r="K46">
+        <f>H46*I46</f>
+        <v>12.913599999999999</v>
+      </c>
+      <c r="M46">
+        <f>200*12</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <f>H46-K46</f>
+        <v>148.50639999999999</v>
       </c>
     </row>
   </sheetData>
@@ -56931,7 +56951,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -56974,7 +56994,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -56987,7 +57007,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -57002,7 +57022,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -57015,7 +57035,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -57024,7 +57044,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -57064,7 +57084,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -57081,7 +57101,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -57093,7 +57113,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -57150,7 +57170,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -57179,7 +57199,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -57243,7 +57263,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -57252,7 +57272,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -57266,7 +57286,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -57285,7 +57305,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -57297,7 +57317,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -57306,7 +57326,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -57317,7 +57337,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -57467,7 +57487,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -57540,7 +57560,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -57685,7 +57705,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -57831,27 +57851,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -57889,24 +57909,18 @@
       </c>
       <c r="Q23" s="319"/>
       <c r="S23" s="269">
-        <v>0.05</v>
-      </c>
-      <c r="T23" s="270">
-        <f>+T22</f>
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="U23" s="270">
-        <f>+U22</f>
-        <v>5.0999999999999997E-2</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="T23" s="270"/>
+      <c r="U23" s="270"/>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -57918,7 +57932,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -57926,7 +57940,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -57968,11 +57982,11 @@
       </c>
       <c r="T24" s="270">
         <f>+T23</f>
-        <v>3.5000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="U24" s="270">
         <f>+U23</f>
-        <v>5.0999999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="V24" s="142">
         <f t="shared" si="6"/>
@@ -58351,7 +58365,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -58394,7 +58408,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -58407,7 +58421,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -58422,7 +58436,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -58435,7 +58449,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -58444,7 +58458,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -58484,7 +58498,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -58501,7 +58515,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -58513,7 +58527,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -58570,7 +58584,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -58599,7 +58613,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -58663,7 +58677,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -58672,7 +58686,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -58686,7 +58700,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -58705,7 +58719,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -58717,7 +58731,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -58726,7 +58740,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -58737,7 +58751,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -58887,7 +58901,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -58960,7 +58974,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -59105,7 +59119,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -59251,27 +59265,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -59321,12 +59335,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -59338,7 +59352,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -59346,7 +59360,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -59771,7 +59785,7 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
     <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -59814,7 +59828,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -59827,7 +59841,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -59842,7 +59856,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -59855,7 +59869,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -59864,7 +59878,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -59904,7 +59918,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -59921,7 +59935,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -59933,7 +59947,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -59990,7 +60004,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -60019,7 +60033,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -60083,7 +60097,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -60092,7 +60106,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -60106,7 +60120,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -60125,7 +60139,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -60137,7 +60151,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -60146,7 +60160,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -60157,7 +60171,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -60307,7 +60321,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -60380,7 +60394,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -60525,7 +60539,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -60671,27 +60685,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -60741,12 +60755,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -60758,7 +60772,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -60766,7 +60780,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
@@ -61191,9 +61205,9 @@
     <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" style="61" customWidth="1"/>
+    <col min="14" max="14" width="10.81640625" style="61" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
-    <col min="16" max="16" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="6.1796875" style="61" customWidth="1"/>
@@ -61234,7 +61248,7 @@
     </row>
     <row r="4" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="370" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B4" s="370"/>
       <c r="C4" s="370"/>
@@ -61247,7 +61261,7 @@
       <c r="M4" s="371"/>
       <c r="N4" s="401">
         <f>'1'!N4:P4</f>
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="O4" s="401"/>
       <c r="P4" s="401"/>
@@ -61262,7 +61276,7 @@
     </row>
     <row r="5" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="398"/>
       <c r="C5" s="398"/>
@@ -61275,7 +61289,7 @@
       <c r="M5" s="371"/>
       <c r="N5" s="401">
         <f>N4-1</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="O5" s="370"/>
       <c r="P5" s="370"/>
@@ -61284,7 +61298,7 @@
     </row>
     <row r="6" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="399" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B6" s="399"/>
       <c r="C6" s="399"/>
@@ -61324,7 +61338,7 @@
       <c r="L7" s="371"/>
       <c r="M7" s="371"/>
       <c r="N7" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O7" s="400"/>
       <c r="P7" s="400"/>
@@ -61341,7 +61355,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="397" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B8" s="397"/>
       <c r="C8" s="397"/>
@@ -61353,7 +61367,7 @@
       <c r="L8" s="371"/>
       <c r="M8" s="371"/>
       <c r="N8" s="400" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O8" s="400"/>
       <c r="P8" s="400"/>
@@ -61410,7 +61424,7 @@
     </row>
     <row r="11" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B11" s="280" t="s">
         <v>80</v>
@@ -61439,7 +61453,7 @@
     </row>
     <row r="12" spans="1:22 16383:16384" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="249" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="241" t="s">
         <v>79</v>
@@ -61503,7 +61517,7 @@
         <v>84</v>
       </c>
       <c r="N14" s="364" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O14" s="103" t="s">
         <v>89</v>
@@ -61512,7 +61526,7 @@
         <v>56</v>
       </c>
       <c r="Q14" s="320" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="XFD14" t="s">
         <v>106</v>
@@ -61526,7 +61540,7 @@
         <v>57</v>
       </c>
       <c r="E15" s="143" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>53</v>
@@ -61545,7 +61559,7 @@
         <v>39</v>
       </c>
       <c r="L15" s="145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M15" s="363"/>
       <c r="N15" s="365"/>
@@ -61557,7 +61571,7 @@
         <v>38</v>
       </c>
       <c r="Q15" s="320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S15" s="295" t="s">
         <v>59</v>
@@ -61566,7 +61580,7 @@
         <v>39</v>
       </c>
       <c r="U15" s="296" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="V15" s="296" t="s">
         <v>35</v>
@@ -61577,7 +61591,7 @@
     </row>
     <row r="16" spans="1:22 16383:16384" x14ac:dyDescent="0.35">
       <c r="A16" s="104" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B16" s="108" t="str">
         <f>VLOOKUP($A16,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -61727,7 +61741,7 @@
     </row>
     <row r="18" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A18" s="82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B18" s="109" t="str">
         <f>VLOOKUP($A18,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -61800,7 +61814,7 @@
     </row>
     <row r="19" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A19" s="82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B19" s="109" t="str">
         <f>VLOOKUP($A19,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -61945,7 +61959,7 @@
     </row>
     <row r="21" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A21" s="82" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B21" s="109" t="str">
         <f>VLOOKUP($A21,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -62091,27 +62105,27 @@
     </row>
     <row r="23" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
       <c r="A23" s="82" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B23" s="109" t="str">
         <f>VLOOKUP($A23,'Cust. Price List'!$D$6:$O$14,2,0)</f>
-        <v>Lemon Tarka (ECO)</v>
+        <v>Indomie Chicken ® 4 in 1</v>
       </c>
       <c r="C23" s="106">
         <f>VLOOKUP(B23,'Cust. Price List'!E13:P21,2,0)</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D23" s="284">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,4,0)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E23" s="291">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,6,0)</f>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F23" s="292">
         <f>VLOOKUP(A23,'Cust. Price List'!D13:M21,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>161.41999999999999</v>
       </c>
       <c r="G23" s="287"/>
       <c r="H23" s="96"/>
@@ -62161,12 +62175,12 @@
       </c>
       <c r="V23" s="142">
         <f t="shared" si="6"/>
-        <v>7.6271186440677923</v>
+        <v>30.508474576271169</v>
       </c>
     </row>
     <row r="24" spans="1:22 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="80" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B24" s="110" t="str">
         <f>VLOOKUP($A24,'Cust. Price List'!$D$6:$O$14,2,0)</f>
@@ -62178,7 +62192,7 @@
       </c>
       <c r="D24" s="285">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,4,0)</f>
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E24" s="293">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,6,0)</f>
@@ -62186,7 +62200,7 @@
       </c>
       <c r="F24" s="294">
         <f>VLOOKUP(A24,'Cust. Price List'!D14:M22,10,0)</f>
-        <v>39.230000000000004</v>
+        <v>32.69166666666667</v>
       </c>
       <c r="G24" s="288"/>
       <c r="H24" s="97"/>
